--- a/tame_output/ON/bt/strategyON_20231105.xlsx
+++ b/tame_output/ON/bt/strategyON_20231105.xlsx
@@ -595,12 +595,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>49.6%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -610,11 +610,11 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1768</v>
+        <v>1769</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2023-11-03</t>
+          <t>2023-11-04</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>84.4%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>79.8%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -758,16 +758,16 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1768</v>
+        <v>1769</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2023-11-03</t>
+          <t>2023-11-04</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>20.2%</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>30.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1768</v>
+        <v>1769</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2023-11-03</t>
+          <t>2023-11-04</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>12.3%</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>102.7%</t>
+          <t>102.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1768</v>
+        <v>1769</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2023-11-03</t>
+          <t>2023-11-04</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>25.1%</t>
         </is>
       </c>
     </row>
@@ -1212,12 +1212,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>24.5%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1768</v>
+        <v>1769</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2023-11-03</t>
+          <t>2023-11-04</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>132.9%</t>
+          <t>133.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1768</v>
+        <v>1769</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2023-11-03</t>
+          <t>2023-11-04</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>126.9%</t>
+          <t>127.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1771"/>
+  <dimension ref="A1:G1772"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42243,7 +42243,7 @@
         <v>45233</v>
       </c>
       <c r="B1771" t="n">
-        <v>3.068083032765877</v>
+        <v>3.069025022408316</v>
       </c>
       <c r="C1771" t="n">
         <v>3.051179068073428</v>
@@ -42259,6 +42259,29 @@
       </c>
       <c r="G1771" t="n">
         <v>4.354872249760345</v>
+      </c>
+    </row>
+    <row r="1772">
+      <c r="A1772" s="2" t="n">
+        <v>45234</v>
+      </c>
+      <c r="B1772" t="n">
+        <v>3.079731783294786</v>
+      </c>
+      <c r="C1772" t="n">
+        <v>3.056704057212575</v>
+      </c>
+      <c r="D1772" t="n">
+        <v>1.546856854070063</v>
+      </c>
+      <c r="E1772" t="n">
+        <v>3.675090374526853</v>
+      </c>
+      <c r="F1772" t="n">
+        <v>2.172821969478192</v>
+      </c>
+      <c r="G1772" t="n">
+        <v>4.360397238899492</v>
       </c>
     </row>
   </sheetData>
